--- a/AAII_Financials/Quarterly/LU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>LU</t>
   </si>
@@ -656,218 +656,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>919300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>905400</v>
+      </c>
+      <c r="F8" s="3">
         <v>1137300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1117400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>983000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>970500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1353700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>790300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>697700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>964400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2014300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1103300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1278300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1467100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1736900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1822800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2125100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2407300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2181500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2263900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2107500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2194600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1849500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1918700</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>4</v>
       </c>
@@ -877,62 +885,68 @@
       <c r="AD8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>0</v>
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>130100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>128100</v>
+      </c>
+      <c r="F9" s="3">
         <v>766900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>753500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>143000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>141200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1158000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>156300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>188700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>183800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1139500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>202500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>217300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>226800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
@@ -981,53 +995,59 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>789200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>777200</v>
+      </c>
+      <c r="F10" s="3">
         <v>370400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>363900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>840000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>829300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>195600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>634000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>509000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>780600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>874800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>900800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1060900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1240300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1076,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,103 +1335,115 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>33800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>9400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>48900</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>95000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>58200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>1100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1405,44 +1451,44 @@
         <v>1800</v>
       </c>
       <c r="E15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G15" s="3">
         <v>3700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3600</v>
       </c>
       <c r="H15" s="3">
         <v>3600</v>
       </c>
       <c r="I15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K15" s="3">
         <v>6500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>6300</v>
       </c>
       <c r="L15" s="3">
         <v>6400</v>
       </c>
       <c r="M15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N15" s="3">
+        <v>6400</v>
+      </c>
+      <c r="O15" s="3">
         <v>6100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>6100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>6500</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1491,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,178 +1575,186 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>963100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>948500</v>
+      </c>
+      <c r="F17" s="3">
         <v>463600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>455500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>938500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>926600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>309800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>891400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>845600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>892200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>347200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1048600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1096400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1283600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1810100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1487900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1416200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1400000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1587800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1393600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1208600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1164500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1249200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1171000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1221800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1161000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1115000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1027300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>991100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1147000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>824000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="F18" s="3">
         <v>673700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>661900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>44500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>43900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1043900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-101100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-147800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>72300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1667100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>54700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>181900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>183500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-73200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>334800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>708900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1007300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>593700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>870200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>898900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1030100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>600300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>747600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1704,17 +1764,23 @@
       <c r="AD18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-991100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1147000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-824000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,83 +1814,85 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="F20" s="3">
         <v>530700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>521400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>686600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-7200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>38900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>765400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>7600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-18000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-6200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-43200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-103700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-13000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-19000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-64900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-214000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1834,65 +1902,71 @@
       <c r="AD20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1853700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1740600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1654600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F21" s="3">
         <v>144800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>144200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>43700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>43100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>360900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-87500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-180300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>76300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>908000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>53100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>206000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>196100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-58500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1938,53 +2012,59 @@
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F22" s="3">
         <v>269200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>264400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>662300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>-3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1247500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>18700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>27500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2025,206 +2105,224 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>61900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>54300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-50500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-76400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-75100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>34300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>33800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-197700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-102400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-183500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>61900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-153200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>41600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>181100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>162200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>291700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>605100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>994400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>597900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>851300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>902800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>965200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>581900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>533600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>640400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>909000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>545900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>731800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>793000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>800800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>539300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>798000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>600</v>
+      </c>
+      <c r="F24" s="3">
         <v>8900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>70500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>69600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-17100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>18400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>176900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-35800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>23600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>42800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>55600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>28600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>104500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>196900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>259000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>198900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>266200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>230700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>251600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>185500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>215800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>185700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>248600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>161400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>199200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>231800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>210400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>159400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,83 +2416,89 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-85300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-83800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-36200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-35800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-180600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-103400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-201900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-114900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-117400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>17900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>138400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>106600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>187200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>408200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>735400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>399100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>585000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>672200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>713600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>396400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>317900</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>4</v>
       </c>
@@ -2404,92 +2508,98 @@
       <c r="AD26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>0</v>
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-95100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-93400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-53500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-52900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-182700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-124700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-204400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-120600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-119100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>12900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>133100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>97800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-114900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>183300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>404400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>733900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>400400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>587000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>678600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>717400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>401800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>321900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>4</v>
       </c>
@@ -2499,17 +2609,23 @@
       <c r="AD27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>0</v>
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,83 +3022,89 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-530700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-521400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-686600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>7200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-38900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-765400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-7600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>18000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>6200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>11800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>43200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>103700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>13000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>19000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>64900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>18400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>214000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2974,92 +3114,98 @@
       <c r="AD32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1853700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1740600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1654600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-95100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-93400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-53500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-52900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-182700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-124700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-204400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-120600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-119100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>12900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>133100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>97800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-114900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>183300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>404400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>733900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>400400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>587000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>678600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>717400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>401800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>321900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>4</v>
       </c>
@@ -3069,17 +3215,23 @@
       <c r="AD33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>0</v>
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,83 +3325,89 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-95100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-93400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-53500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-52900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-182700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-124700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-204400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-120600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-119100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>12900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>133100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>97800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-114900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>183300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>404400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>733900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>400400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>587000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>678600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>717400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>401800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>321900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3259,117 +3417,129 @@
       <c r="AD35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>0</v>
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,86 +3610,88 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2828400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2785500</v>
+      </c>
+      <c r="F41" s="3">
         <v>3157700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3102300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3893300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3843600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4096900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3854700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5107300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5462500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5584500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5452000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6470800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7468500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6186500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6328100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5958800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5638100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4786900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4342400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4125400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3520600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3362900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2118500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2285500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3533,53 +3707,59 @@
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>225500</v>
+        <v>4920000</v>
       </c>
       <c r="E42" s="3">
-        <v>221500</v>
+        <v>4845400</v>
       </c>
       <c r="F42" s="3">
-        <v>290800</v>
+        <v>5181800</v>
       </c>
       <c r="G42" s="3">
-        <v>287100</v>
+        <v>5091000</v>
       </c>
       <c r="H42" s="3">
-        <v>90000</v>
+        <v>4176600</v>
       </c>
       <c r="I42" s="3">
+        <v>4123200</v>
+      </c>
+      <c r="J42" s="3">
+        <v>2878800</v>
+      </c>
+      <c r="K42" s="3">
         <v>4388400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4025000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4549400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>4074600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3444300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3195500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3413500</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3628,59 +3808,65 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15282500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>15050800</v>
+      </c>
+      <c r="F43" s="3">
         <v>14981300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14718600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14703800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14516000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>15832000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>16523800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>15847000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>17015600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>18842300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>21404500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>23104000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>28614200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>328800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>349900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3690,11 +3876,11 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3723,8 +3909,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3764,11 +3956,11 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3818,59 +4010,65 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>209700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>206500</v>
+      </c>
+      <c r="F45" s="3">
         <v>268700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>264000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>263800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>260400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>299300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>333500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>528500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>692200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>112700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>33900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3880,11 +4078,11 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3913,53 +4111,59 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21415700</v>
+        <v>25808300</v>
       </c>
       <c r="E46" s="3">
-        <v>21040300</v>
+        <v>25416900</v>
       </c>
       <c r="F46" s="3">
-        <v>20586900</v>
+        <v>26372000</v>
       </c>
       <c r="G46" s="3">
-        <v>20323900</v>
+        <v>25909700</v>
       </c>
       <c r="H46" s="3">
-        <v>22320000</v>
+        <v>24472700</v>
       </c>
       <c r="I46" s="3">
+        <v>24160100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>25108800</v>
+      </c>
+      <c r="K46" s="3">
         <v>26431700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>26856900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29058200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>30750400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>32816100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>35865900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>44328000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4008,86 +4212,92 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5840200</v>
+        <v>1256200</v>
       </c>
       <c r="E47" s="3">
-        <v>5737800</v>
+        <v>1237200</v>
       </c>
       <c r="F47" s="3">
-        <v>4166400</v>
+        <v>883900</v>
       </c>
       <c r="G47" s="3">
-        <v>4113200</v>
+        <v>868400</v>
       </c>
       <c r="H47" s="3">
-        <v>3152600</v>
+        <v>280600</v>
       </c>
       <c r="I47" s="3">
+        <v>277000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>363800</v>
+      </c>
+      <c r="K47" s="3">
         <v>551700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>640900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>406900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>425100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>418400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>505600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>540400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>36416000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>38447900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>39597800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>40045000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>38318200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>38198400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>34030000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>30471500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>25797900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>23603900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>20430200</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4103,86 +4313,92 @@
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>39200</v>
+      </c>
+      <c r="F48" s="3">
         <v>45700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>44900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>43200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>42600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>50800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>65800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>70500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>76300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>82000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>92500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>111100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>141500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>151800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>149100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>157200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>153500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>163300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>164800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>171700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>184500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>194500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>217100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>220000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4198,86 +4414,92 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1482000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1459500</v>
+      </c>
+      <c r="F49" s="3">
         <v>1441200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1416000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1412500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1394400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1388100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1448100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1402000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1355800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1380100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1341500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1350000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1425700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1381100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1355400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1364200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1364600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1352700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1493400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1552100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1568800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1521400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1610500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1615900</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
@@ -4293,8 +4515,14 @@
       <c r="AG49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,86 +4717,92 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F52" s="3">
         <v>13000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>12700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>141700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>139800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>44600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>82000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>127900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>170200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>188500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>209200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>226700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4594100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4450500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4124600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5126400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4867300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3145000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3921500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4339000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3673200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3245600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3607300</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4578,8 +4818,14 @@
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,86 +4919,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29840400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>29387900</v>
+      </c>
+      <c r="F54" s="3">
         <v>29754500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29232900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27274900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>26926500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>27885200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29431800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29851800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31840700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33426400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>35520200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>38730000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>47399500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>49239100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>51211700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>51529100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>52547200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>49660500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>47507500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>43916400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>40203300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>34645500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>30902000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>28313500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4768,8 +5020,14 @@
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,86 +5098,88 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F57" s="3">
         <v>17900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>11100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>862400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>808200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>19600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1115700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>14800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1234200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>25195500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>27023800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>29404600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>29687300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>28521600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>26924600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>24017200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>20979300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>17395300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>15833700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>14344100</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4933,59 +5195,65 @@
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>58500</v>
+      </c>
+      <c r="F58" s="3">
         <v>98600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>96900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>111900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>110500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>139500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>105200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>134300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>237600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>313200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6713800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5298300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4998,11 +5266,11 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5028,86 +5296,92 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>241800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>238200</v>
+      </c>
+      <c r="F59" s="3">
         <v>238400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>234200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>220600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>217800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>319500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>220700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1653600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>219500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>623100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>246300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>739900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>407000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1795600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1651500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>275900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1025700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1132900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>411100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>308200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>407000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>363400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>251600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>194400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5123,53 +5397,59 @@
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>745900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>734600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1032400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1014300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>806100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>795800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1146000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1083100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2197600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1027700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1419200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1362000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1391600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1954400</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5218,86 +5498,92 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10619200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10458100</v>
+      </c>
+      <c r="F61" s="3">
         <v>10029100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9853300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8333500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8227000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7864600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6785200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6501200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6679400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6290000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5907700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6431300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7509900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>774300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2919000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7310100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7049400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6172100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5642200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5410600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4848500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4028800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4556300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4133800</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5313,86 +5599,92 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6451200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6353400</v>
+      </c>
+      <c r="F62" s="3">
         <v>6920900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>6799600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>6446600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>6364200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7375700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>9198200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9717100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>11201300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12431400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>15247800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>17743600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>24000800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>113700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>145900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>140900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>133900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>114900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>633900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>666600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>760500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>798100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>837400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>793600</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5408,8 +5700,14 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,86 +6003,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17850000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17579300</v>
+      </c>
+      <c r="F66" s="3">
         <v>18024900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17709000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>15674900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>15474700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16432000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>17122900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18474700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18984900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20214500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>22592900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25655800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33574300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>36101200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>38292400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>38227900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>38876900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>36839600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>34455400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>31186500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>27766600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>23292400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>22157200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>20173100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5788,8 +6104,14 @@
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,86 +6545,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8214900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8090400</v>
+      </c>
+      <c r="F72" s="3">
         <v>8741200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8587900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8100300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7996800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>8663700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>8974200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>8782900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>8949100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>9634100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>9090700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>9133300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9502200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9377300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9302700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>10119100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9810100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>8989900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>8853500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>8266500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>7666500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6729800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>6665100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>6060600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6298,8 +6646,14 @@
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,86 +6949,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11635200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11458800</v>
+      </c>
+      <c r="F76" s="3">
         <v>11413400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11213400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11310600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11166100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11203100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12053200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11151000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12636700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12994500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12717700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12868300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13583900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13137900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12919200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>13301300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13670300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>12820900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13052100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>12729900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>12436700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>11353100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>8744800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>8140300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6678,8 +7050,14 @@
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,183 +7151,195 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-95100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-93400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-53500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-52900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-182700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-124700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-204400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-120600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-119100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>12900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>133100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>97800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-114900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>183300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>404400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>733900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>400400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>587000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>678600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>717400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>401800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>321900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>4</v>
       </c>
@@ -6959,17 +7349,23 @@
       <c r="AD81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>0</v>
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,56 +7399,58 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>53200</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>83900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>109600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>26500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
@@ -7065,11 +7463,11 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -7077,14 +7475,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -7098,8 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,83 +8001,89 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="F89" s="3">
         <v>505000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>496100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>377500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>372700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-299600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>71800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-222800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>69600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>661700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>693100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>275000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>478400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>680000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>327300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-143900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-236600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-86700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>243500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>301300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>256300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-331000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>740200</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>4</v>
       </c>
@@ -7659,17 +8093,23 @@
       <c r="AD89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,52 +8143,54 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-9900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7777,14 +8219,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7798,8 +8240,14 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,83 +8442,89 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>109100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-976300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-959200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-196100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-193600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>276700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-266900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>607000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>380500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-572700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-508800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-46800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>316600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>149900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-768100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>840900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>958600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>406400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>364300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-193100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-551500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-720500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1393800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8074,17 +8534,23 @@
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,16 +8584,18 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>3700</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
@@ -8135,39 +8603,39 @@
       <c r="G96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>703200</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>202400</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>108400</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8213,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,83 +8984,89 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-144200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="F100" s="3">
         <v>320000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>314400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-80900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-79900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>257200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1278800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-645900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>69100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-124100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1103800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1219500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-404300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-997500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>616100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-914400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-100800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-224800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-441000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>51700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>276100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2508100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>458600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8584,92 +9076,98 @@
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-13500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>10800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-14100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>10700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>54200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-21600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>28600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>3700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>28100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-13600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>2500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-12100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-98200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>29000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>4</v>
       </c>
@@ -8679,92 +9177,98 @@
       <c r="AD101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>0</v>
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-79100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-152400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-149700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>99300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>98000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>237900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1487400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-250900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>520100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-49200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-908800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-937000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>395600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-188500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>203300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-214000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>618000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>81300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>169300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>147800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-15800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1358300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-166000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
@@ -8774,13 +9278,19 @@
       <c r="AD102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
